--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HOMS U.E.MATARÓ.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HOMS U.E.MATARÓ.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>28.5762</v>
+        <v>40.2481</v>
       </c>
       <c r="E2" t="n">
-        <v>40.4429</v>
+        <v>48.3539</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.8669</v>
+        <v>-8.106</v>
       </c>
       <c r="G2" t="n">
         <v>42.0905</v>
@@ -610,13 +610,13 @@
         <v>50.7193</v>
       </c>
       <c r="S2" t="n">
-        <v>-16.7519</v>
+        <v>-5.079899999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-10.8611</v>
+        <v>-2.9496</v>
       </c>
       <c r="U2" t="n">
-        <v>-5.8909</v>
+        <v>-2.1305</v>
       </c>
       <c r="V2" t="n">
         <v>39.9939</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3465</v>
+        <v>3.442</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0145</v>
+        <v>4.0804</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6681</v>
+        <v>-0.6384</v>
       </c>
       <c r="G3" t="n">
         <v>2.2307</v>
@@ -688,13 +688,13 @@
         <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6435</v>
+        <v>0.739</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9917</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2824</v>
+        <v>-0.2527</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3491</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>X. MAYO PERIAGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.728</v>
+        <v>0.1523</v>
       </c>
       <c r="E4" t="n">
-        <v>19.537</v>
+        <v>-0.6197</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.809</v>
+        <v>0.772</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.5644</v>
+        <v>0.0389</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2772000000000001</v>
+        <v>0.3179</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.8411</v>
+        <v>-0.2789</v>
       </c>
       <c r="J4" t="n">
-        <v>24.4476</v>
+        <v>-0.6584</v>
       </c>
       <c r="K4" t="n">
-        <v>16.2783</v>
+        <v>0.0389</v>
       </c>
       <c r="L4" t="n">
-        <v>8.169600000000001</v>
+        <v>-0.6974</v>
       </c>
       <c r="M4" t="n">
-        <v>-35.0119</v>
+        <v>0.6974</v>
       </c>
       <c r="N4" t="n">
-        <v>-16.0016</v>
+        <v>0.2789</v>
       </c>
       <c r="O4" t="n">
-        <v>-19.0103</v>
+        <v>0.4184</v>
       </c>
       <c r="P4" t="n">
-        <v>6.9815</v>
+        <v>0.2053</v>
       </c>
       <c r="Q4" t="n">
-        <v>-34.0868</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>41.0686</v>
+        <v>0.2053</v>
       </c>
       <c r="S4" t="n">
-        <v>15.2438</v>
+        <v>-0.092</v>
       </c>
       <c r="T4" t="n">
-        <v>14.4619</v>
+        <v>0.0387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7819000000000002</v>
+        <v>-0.1307</v>
       </c>
       <c r="V4" t="n">
-        <v>-9.9336</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>14.714</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-24.6479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. MAYO PERIAGO</t>
+          <t>A. VENTURA PEDREÑO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1071</v>
+        <v>-6.891500000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7902</v>
+        <v>-0.707099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6830000000000001</v>
+        <v>-6.1844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0389</v>
+        <v>-3.3331</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3179</v>
+        <v>-5.7422</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2789</v>
+        <v>2.408999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6584</v>
+        <v>15.8862</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0389</v>
+        <v>5.682700000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6974</v>
+        <v>10.2036</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6974</v>
+        <v>-19.2192</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2789</v>
+        <v>-11.4246</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4184</v>
+        <v>-7.7944</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2053</v>
+        <v>-0.8212999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-20.1234</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2053</v>
+        <v>19.3021</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3514</v>
+        <v>-2.6326</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1317</v>
+        <v>-2.5167</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2197</v>
+        <v>-0.116</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1042000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>6.0471</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-6.1513</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ROKER</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7663</v>
+        <v>-8.8317</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0216</v>
+        <v>9.061500000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7879</v>
+        <v>-17.8932</v>
       </c>
       <c r="G6" t="n">
-        <v>12.0066</v>
+        <v>-10.5644</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4283</v>
+        <v>0.2772000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5784</v>
+        <v>-10.8411</v>
       </c>
       <c r="J6" t="n">
-        <v>12.9463</v>
+        <v>24.4476</v>
       </c>
       <c r="K6" t="n">
-        <v>10.6178</v>
+        <v>16.2783</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3284</v>
+        <v>8.169600000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9397</v>
+        <v>-35.0119</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1896</v>
+        <v>-16.0016</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2497</v>
+        <v>-19.0103</v>
       </c>
       <c r="P6" t="n">
-        <v>-8.4192</v>
+        <v>6.9815</v>
       </c>
       <c r="Q6" t="n">
-        <v>-17.0434</v>
+        <v>-34.0868</v>
       </c>
       <c r="R6" t="n">
-        <v>8.6244</v>
+        <v>41.0686</v>
       </c>
       <c r="S6" t="n">
-        <v>6.226</v>
+        <v>4.6845</v>
       </c>
       <c r="T6" t="n">
-        <v>4.4619</v>
+        <v>3.9865</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7642</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-12.5797</v>
+        <v>-9.9336</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6568000000000001</v>
+        <v>14.714</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.2367</v>
+        <v>-24.6479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>A. ROKER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.804099999999999</v>
+        <v>-8.9008</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.440399999999999</v>
+        <v>-2.6124</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3637</v>
+        <v>-6.288499999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-10.8851</v>
+        <v>12.0066</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.9655</v>
+        <v>8.4283</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.9198</v>
+        <v>3.5784</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2267</v>
+        <v>12.9463</v>
       </c>
       <c r="K7" t="n">
-        <v>4.0312</v>
+        <v>10.6178</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1955</v>
+        <v>2.3284</v>
       </c>
       <c r="M7" t="n">
-        <v>-15.1118</v>
+        <v>-0.9397</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.9964</v>
+        <v>-2.1896</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.1153</v>
+        <v>1.2497</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4374</v>
+        <v>-8.4192</v>
       </c>
       <c r="Q7" t="n">
-        <v>-13.1418</v>
+        <v>-17.0434</v>
       </c>
       <c r="R7" t="n">
-        <v>14.5794</v>
+        <v>8.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7045</v>
+        <v>0.09139999999999993</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0476</v>
+        <v>0.8279999999999998</v>
       </c>
       <c r="U7" t="n">
-        <v>3.6564</v>
+        <v>-0.7363000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0607</v>
+        <v>-12.5797</v>
       </c>
       <c r="W7" t="n">
-        <v>3.427</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.4877</v>
+        <v>-13.2367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>-10.1762</v>
+        <v>-10.0082</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.943800000000001</v>
+        <v>-5.1876</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2322000000000004</v>
+        <v>-4.8204</v>
       </c>
       <c r="G8" t="n">
-        <v>-11.1045</v>
+        <v>-10.8851</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.207</v>
+        <v>-4.9655</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8974</v>
+        <v>-5.9198</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1032</v>
+        <v>4.2267</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3305999999999999</v>
+        <v>4.0312</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7725999999999998</v>
+        <v>0.1955</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.2076</v>
+        <v>-15.1118</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.5377</v>
+        <v>-8.9964</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.670199999999999</v>
+        <v>-6.1153</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6160999999999999</v>
+        <v>1.4374</v>
       </c>
       <c r="Q8" t="n">
-        <v>-14.374</v>
+        <v>-13.1418</v>
       </c>
       <c r="R8" t="n">
-        <v>13.7578</v>
+        <v>14.5794</v>
       </c>
       <c r="S8" t="n">
-        <v>5.2898</v>
+        <v>1.5004</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8158</v>
+        <v>0.3005</v>
       </c>
       <c r="U8" t="n">
-        <v>4.474</v>
+        <v>1.1998</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.7451</v>
+        <v>-2.0607</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5111</v>
+        <v>3.427</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.256399999999999</v>
+        <v>-5.4877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VENTURA PEDREÑO</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.7986</v>
+        <v>-13.6894</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.051</v>
+        <v>6.134399999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.747400000000001</v>
+        <v>-19.8237</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3331</v>
+        <v>-1.0521</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.7422</v>
+        <v>-7.4376</v>
       </c>
       <c r="I9" t="n">
-        <v>2.408999999999999</v>
+        <v>6.3855</v>
       </c>
       <c r="J9" t="n">
-        <v>15.8862</v>
+        <v>15.5849</v>
       </c>
       <c r="K9" t="n">
-        <v>5.682700000000001</v>
+        <v>1.5</v>
       </c>
       <c r="L9" t="n">
-        <v>10.2036</v>
+        <v>14.0851</v>
       </c>
       <c r="M9" t="n">
-        <v>-19.2192</v>
+        <v>-16.637</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.4246</v>
+        <v>-8.9374</v>
       </c>
       <c r="O9" t="n">
-        <v>-7.7944</v>
+        <v>-7.6996</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8212999999999999</v>
+        <v>7.1867</v>
       </c>
       <c r="Q9" t="n">
-        <v>-20.1234</v>
+        <v>-14.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>19.3021</v>
+        <v>21.3555</v>
       </c>
       <c r="S9" t="n">
-        <v>-7.539400000000001</v>
+        <v>-7.0971</v>
       </c>
       <c r="T9" t="n">
-        <v>-4.8607</v>
+        <v>-2.8341</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.6787</v>
+        <v>-4.2631</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1042000000000001</v>
+        <v>-12.7269</v>
       </c>
       <c r="W9" t="n">
-        <v>6.0471</v>
+        <v>7.5522</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.1513</v>
+        <v>-20.2792</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.5369</v>
+        <v>-13.9275</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.4674</v>
+        <v>-11.3656</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0695</v>
+        <v>-2.561900000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.5282</v>
+        <v>-11.1045</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.8368</v>
+        <v>-7.207</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3084</v>
+        <v>-3.8974</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2412</v>
+        <v>1.1032</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.149</v>
+        <v>0.3305999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9077999999999999</v>
+        <v>0.7725999999999998</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.287</v>
+        <v>-12.2076</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6878</v>
+        <v>-7.5377</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5993999999999999</v>
+        <v>-4.670199999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.0351</v>
+        <v>-0.6160999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.4992</v>
+        <v>-14.374</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4641</v>
+        <v>13.7578</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5151</v>
+        <v>1.5385</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3819</v>
+        <v>-0.6059000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1333</v>
+        <v>2.1444</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4886</v>
+        <v>-3.7451</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1089</v>
+        <v>2.5111</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3797</v>
+        <v>-6.256399999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.1409</v>
+        <v>-14.6698</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9378</v>
+        <v>-12.5323</v>
       </c>
       <c r="F11" t="n">
-        <v>-21.0788</v>
+        <v>-2.1375</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0521</v>
+        <v>-4.5282</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.4376</v>
+        <v>-4.8368</v>
       </c>
       <c r="I11" t="n">
-        <v>6.3855</v>
+        <v>0.3084</v>
       </c>
       <c r="J11" t="n">
-        <v>15.5849</v>
+        <v>-2.2412</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5</v>
+        <v>-3.149</v>
       </c>
       <c r="L11" t="n">
-        <v>14.0851</v>
+        <v>0.9077999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-16.637</v>
+        <v>-2.287</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.9374</v>
+        <v>-1.6878</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.6996</v>
+        <v>-0.5993999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>7.1867</v>
+        <v>-9.0351</v>
       </c>
       <c r="Q11" t="n">
-        <v>-14.1684</v>
+        <v>-11.4992</v>
       </c>
       <c r="R11" t="n">
-        <v>21.3555</v>
+        <v>2.4641</v>
       </c>
       <c r="S11" t="n">
-        <v>-11.5489</v>
+        <v>1.3822</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.0303</v>
+        <v>1.3169</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.5183</v>
+        <v>0.06519999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>-12.7269</v>
+        <v>-2.4886</v>
       </c>
       <c r="W11" t="n">
-        <v>7.5522</v>
+        <v>-0.1089</v>
       </c>
       <c r="X11" t="n">
-        <v>-20.2792</v>
+        <v>-2.3797</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.0754</v>
+        <v>-15.3762</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0994</v>
+        <v>-3.3089</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.9761</v>
+        <v>-12.0674</v>
       </c>
       <c r="G12" t="n">
         <v>-7.7361</v>
@@ -1390,13 +1390,13 @@
         <v>22.177</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.474299999999999</v>
+        <v>-4.7751</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.2649</v>
+        <v>-2.4745</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.2092</v>
+        <v>-2.3004</v>
       </c>
       <c r="V12" t="n">
         <v>-7.3824</v>
@@ -1423,13 +1423,13 @@
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.0714</v>
+        <v>-18.8145</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3162</v>
+        <v>-2.4638</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.7553</v>
+        <v>-16.3508</v>
       </c>
       <c r="G13" t="n">
         <v>6.3994</v>
@@ -1468,13 +1468,13 @@
         <v>18.0701</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.3245</v>
+        <v>-2.0677</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02539999999999992</v>
+        <v>0.8776999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.35</v>
+        <v>-2.9455</v>
       </c>
       <c r="V13" t="n">
         <v>-17.3964</v>
@@ -1501,13 +1501,13 @@
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.8761</v>
+        <v>-21.4098</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.3991</v>
+        <v>-7.865299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.4768</v>
+        <v>-13.5445</v>
       </c>
       <c r="G14" t="n">
         <v>-25.9295</v>
@@ -1546,13 +1546,13 @@
         <v>39.4257</v>
       </c>
       <c r="S14" t="n">
-        <v>-11.4621</v>
+        <v>-5.9953</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.5144</v>
+        <v>-0.9804</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.9477</v>
+        <v>-5.0148</v>
       </c>
       <c r="V14" t="n">
         <v>24.2731</v>
@@ -1579,13 +1579,13 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-28.2028</v>
+        <v>-28.4861</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.2373</v>
+        <v>-13.7962</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.9656</v>
+        <v>-14.6901</v>
       </c>
       <c r="G15" t="n">
         <v>-20.6999</v>
@@ -1624,13 +1624,13 @@
         <v>16.8383</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9196999999999997</v>
+        <v>0.6364999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.2215</v>
+        <v>-1.7801</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1414</v>
+        <v>2.4164</v>
       </c>
       <c r="V15" t="n">
         <v>-7.806699999999999</v>
@@ -1657,13 +1657,13 @@
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-39.7954</v>
+        <v>-32.0692</v>
       </c>
       <c r="E16" t="n">
-        <v>-24.667</v>
+        <v>-19.5649</v>
       </c>
       <c r="F16" t="n">
-        <v>-15.1283</v>
+        <v>-12.5043</v>
       </c>
       <c r="G16" t="n">
         <v>-19.3765</v>
@@ -1702,13 +1702,13 @@
         <v>15.4005</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.3333</v>
+        <v>-6.6066</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.866400000000001</v>
+        <v>-2.7639</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.4669</v>
+        <v>-3.8429</v>
       </c>
       <c r="V16" t="n">
         <v>0.07449999999999926</v>
@@ -1735,13 +1735,13 @@
         <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-45.36360000000001</v>
+        <v>-34.2924</v>
       </c>
       <c r="E17" t="n">
-        <v>-28.7232</v>
+        <v>-22.5902</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.6404</v>
+        <v>-11.7026</v>
       </c>
       <c r="G17" t="n">
         <v>-1.038</v>
@@ -1780,13 +1780,13 @@
         <v>41.6846</v>
       </c>
       <c r="S17" t="n">
-        <v>-17.4555</v>
+        <v>-6.3844</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.128299999999999</v>
+        <v>-2.9952</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.3271</v>
+        <v>-3.3894</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4075</v>
@@ -1813,22 +1813,22 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-210.0641</v>
+        <v>-183.5247</v>
       </c>
       <c r="E18" t="n">
-        <v>-46.1812</v>
+        <v>-34.98379999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-163.883</v>
+        <v>-148.5417</v>
       </c>
       <c r="G18" t="n">
         <v>-53.4813</v>
       </c>
       <c r="H18" t="n">
-        <v>-36.93990000000001</v>
+        <v>-36.9399</v>
       </c>
       <c r="I18" t="n">
-        <v>-16.5411</v>
+        <v>-16.54109999999999</v>
       </c>
       <c r="J18" t="n">
         <v>205.6631</v>
@@ -1849,7 +1849,7 @@
         <v>-103.786</v>
       </c>
       <c r="P18" t="n">
-        <v>-86.24380000000001</v>
+        <v>-86.24379999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>-412.7367</v>
@@ -1858,13 +1858,13 @@
         <v>326.4941</v>
       </c>
       <c r="S18" t="n">
-        <v>-56.6989</v>
+        <v>-30.1582</v>
       </c>
       <c r="T18" t="n">
-        <v>-22.7589</v>
+        <v>-11.5604</v>
       </c>
       <c r="U18" t="n">
-        <v>-33.9397</v>
+        <v>-18.5984</v>
       </c>
       <c r="V18" t="n">
         <v>-13.6394</v>
